--- a/data/trans_dic/AIRE_1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/AIRE_1_R-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>71,28; 92,69</t>
+          <t>72,83; 93,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>75,96; 94,72</t>
+          <t>76,67; 94,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77,84; 92,24</t>
+          <t>78,29; 92,16</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>74,55; 95,32</t>
+          <t>74,92; 95,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,5; 80,68</t>
+          <t>50,29; 81,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,9; 89,43</t>
+          <t>67,76; 88,77</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54,55; 82,38</t>
+          <t>54,26; 81,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69,45; 90,94</t>
+          <t>69,85; 90,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,09; 83,37</t>
+          <t>66,34; 84,01</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>58,66; 89,58</t>
+          <t>59,87; 88,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38,58; 79,61</t>
+          <t>38,02; 78,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53,99; 79,97</t>
+          <t>55,67; 81,58</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,66; 52,26</t>
+          <t>24,4; 50,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34,47; 62,72</t>
+          <t>32,68; 62,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,7; 52,73</t>
+          <t>32,58; 53,0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71,78; 95,22</t>
+          <t>70,72; 94,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>57,34; 83,43</t>
+          <t>59,53; 84,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68,52; 86,01</t>
+          <t>67,22; 85,41</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>53,56; 75,46</t>
+          <t>54,05; 76,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>44,59; 64,51</t>
+          <t>44,1; 64,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50,9; 66,5</t>
+          <t>51,01; 66,31</t>
         </is>
       </c>
     </row>
@@ -921,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>76,37; 92,08</t>
+          <t>76,86; 92,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>88,9; 97,64</t>
+          <t>88,74; 97,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>86,11; 94,26</t>
+          <t>86,24; 94,1</t>
         </is>
       </c>
     </row>
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>71,87; 82,41</t>
+          <t>71,67; 82,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>68,13; 77,15</t>
+          <t>67,77; 76,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>71,32; 78,33</t>
+          <t>71,32; 78,18</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>28963</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>37084</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>66047</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>24907; 31932</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>32389; 39926</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>59850; 70451</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>67641</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>42128</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>109769</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>58702; 74852</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>30668; 49466</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>94406; 123687</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>20697</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>25700</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>46397</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>15982; 23938</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>21953; 28548</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>40389; 51145</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>22558</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15534</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>38092</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>17651; 26097</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>9935; 20573</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>30961; 45369</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>8639</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>12979</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>21618</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>5821; 11955</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8931; 17003</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>16676; 27133</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>17908</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>24184</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>42092</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>14726; 19717</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>19836; 28279</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>36396; 46243</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>36910</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>43660</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>80569</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>30511; 42984</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>35124; 51716</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>69426; 90250</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>50358</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>80420</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>130779</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>45284; 54359</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>75498; 83163</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>124185; 135498</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>253675</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>281689</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>535363</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>237616; 272868</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>261692; 296993</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>511856; 561089</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/AIRE_1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/AIRE_1_R-Provincia-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>72,83; 93,37</t>
+          <t>72,74; 93,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>76,67; 94,51</t>
+          <t>76,36; 95,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78,29; 92,16</t>
+          <t>78,93; 92,8</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>74,92; 95,54</t>
+          <t>74,21; 95,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50,29; 81,12</t>
+          <t>52,0; 80,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,76; 88,77</t>
+          <t>68,24; 88,37</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54,26; 81,28</t>
+          <t>55,56; 83,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69,85; 90,84</t>
+          <t>68,94; 90,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,34; 84,01</t>
+          <t>66,76; 84,51</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,87; 88,51</t>
+          <t>59,97; 89,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38,02; 78,73</t>
+          <t>37,52; 78,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,67; 81,58</t>
+          <t>55,6; 80,28</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,4; 50,1</t>
+          <t>23,58; 51,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,68; 62,22</t>
+          <t>34,24; 63,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,58; 53,0</t>
+          <t>32,82; 52,1</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>70,72; 94,69</t>
+          <t>69,82; 94,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>59,53; 84,87</t>
+          <t>58,09; 84,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>67,22; 85,41</t>
+          <t>67,64; 85,83</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>54,05; 76,14</t>
+          <t>53,79; 76,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>44,1; 64,93</t>
+          <t>43,39; 65,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51,01; 66,31</t>
+          <t>51,88; 66,81</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>76,86; 92,26</t>
+          <t>75,89; 92,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>88,74; 97,75</t>
+          <t>89,56; 97,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>86,24; 94,1</t>
+          <t>85,49; 93,95</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>71,67; 82,3</t>
+          <t>72,36; 82,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>67,77; 76,91</t>
+          <t>68,07; 77,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>71,32; 78,18</t>
+          <t>71,16; 78,17</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24907; 31932</t>
+          <t>24878; 31840</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32389; 39926</t>
+          <t>32260; 40233</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>59850; 70451</t>
+          <t>60342; 70940</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58702; 74852</t>
+          <t>58142; 74860</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30668; 49466</t>
+          <t>31711; 49274</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>94406; 123687</t>
+          <t>95085; 123126</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15982; 23938</t>
+          <t>16365; 24536</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21953; 28548</t>
+          <t>21667; 28471</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40389; 51145</t>
+          <t>40642; 51447</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17651; 26097</t>
+          <t>17680; 26456</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9935; 20573</t>
+          <t>9805; 20444</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30961; 45369</t>
+          <t>30919; 44645</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5821; 11955</t>
+          <t>5627; 12169</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8931; 17003</t>
+          <t>9357; 17356</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16676; 27133</t>
+          <t>16803; 26672</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14726; 19717</t>
+          <t>14539; 19759</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19836; 28279</t>
+          <t>19356; 28152</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36396; 46243</t>
+          <t>36624; 46471</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>30511; 42984</t>
+          <t>30367; 43123</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>35124; 51716</t>
+          <t>34556; 51921</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>69426; 90250</t>
+          <t>70612; 90928</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>45284; 54359</t>
+          <t>44712; 54330</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>75498; 83163</t>
+          <t>76196; 83167</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>124185; 135498</t>
+          <t>123106; 135287</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>237616; 272868</t>
+          <t>239906; 273005</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>261692; 296993</t>
+          <t>262850; 297538</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>511856; 561089</t>
+          <t>510709; 560991</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/AIRE_1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/AIRE_1_R-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>85,22%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>72,74; 93,1</t>
+          <t>74,86; 94,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>76,36; 95,24</t>
+          <t>69,67; 91,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78,93; 92,8</t>
+          <t>76,77; 91,37</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>74,52%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>74,21; 95,55</t>
+          <t>49,44; 81,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52,0; 80,8</t>
+          <t>69,65; 87,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68,24; 88,37</t>
+          <t>63,3; 82,32</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,57%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55,56; 83,3</t>
+          <t>68,43; 90,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68,94; 90,59</t>
+          <t>56,91; 83,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,76; 84,51</t>
+          <t>66,73; 83,7</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,61%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,97; 89,73</t>
+          <t>37,9; 80,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,52; 78,24</t>
+          <t>57,23; 89,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,6; 80,28</t>
+          <t>54,26; 80,41</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>41,26%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>23,58; 51,0</t>
+          <t>33,52; 61,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34,24; 63,51</t>
+          <t>23,76; 50,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,82; 52,1</t>
+          <t>31,53; 51,99</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>78,38%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>69,82; 94,89</t>
+          <t>57,43; 83,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>58,09; 84,49</t>
+          <t>71,88; 95,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>67,64; 85,83</t>
+          <t>69,25; 86,38</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>58,12%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>53,79; 76,39</t>
+          <t>44,61; 64,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>43,39; 65,19</t>
+          <t>50,74; 73,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51,88; 66,81</t>
+          <t>49,94; 65,11</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,62%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>75,89; 92,21</t>
+          <t>88,9; 97,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>89,56; 97,76</t>
+          <t>75,52; 91,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>85,49; 93,95</t>
+          <t>85,88; 94,28</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>73,24%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>72,36; 82,34</t>
+          <t>68,21; 77,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>68,07; 77,05</t>
+          <t>69,37; 77,73</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>71,16; 78,17</t>
+          <t>70,13; 76,2</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28963</t>
+          <t>28614</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37084</t>
+          <t>24271</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66047</t>
+          <t>52885</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24878; 31840</t>
+          <t>24721; 31102</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32260; 40233</t>
+          <t>20226; 26622</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60342; 70940</t>
+          <t>47638; 56701</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>67641</t>
+          <t>37950</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>42128</t>
+          <t>41420</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>109769</t>
+          <t>79370</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58142; 74860</t>
+          <t>26951; 44184</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31711; 49274</t>
+          <t>36217; 45379</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>95085; 123126</t>
+          <t>67421; 87685</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20697</t>
+          <t>22799</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25700</t>
+          <t>20669</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46397</t>
+          <t>43469</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16365; 24536</t>
+          <t>19108; 25303</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21667; 28471</t>
+          <t>16414; 24094</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40642; 51447</t>
+          <t>37878; 47515</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>22558</t>
+          <t>15038</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15534</t>
+          <t>22937</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38092</t>
+          <t>37976</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17680; 26456</t>
+          <t>9545; 20246</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9805; 20444</t>
+          <t>17261; 27013</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30919; 44645</t>
+          <t>30032; 44507</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8639</t>
+          <t>12862</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12979</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21618</t>
+          <t>21408</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5627; 12169</t>
+          <t>9231; 16933</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9357; 17356</t>
+          <t>5784; 12329</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16803; 26672</t>
+          <t>16363; 26975</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>17908</t>
+          <t>21269</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>24184</t>
+          <t>17784</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42092</t>
+          <t>39053</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14539; 19759</t>
+          <t>16752; 24443</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19356; 28152</t>
+          <t>14846; 19655</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36624; 46471</t>
+          <t>34503; 43036</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>51</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>36910</t>
+          <t>40812</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>43660</t>
+          <t>34556</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>80569</t>
+          <t>75369</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>30367; 43123</t>
+          <t>33267; 48022</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>34556; 51921</t>
+          <t>27954; 40639</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>70612; 90928</t>
+          <t>64762; 84429</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>81</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>50358</t>
+          <t>81394</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>80420</t>
+          <t>51513</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>130779</t>
+          <t>132907</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>44712; 54330</t>
+          <t>76480; 84142</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>76196; 83167</t>
+          <t>45800; 55698</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>123106; 135287</t>
+          <t>125961; 138274</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>346</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>253675</t>
+          <t>260739</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>281689</t>
+          <t>221696</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>535363</t>
+          <t>482435</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>239906; 273005</t>
+          <t>244156; 275967</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>262850; 297538</t>
+          <t>208646; 233782</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>510709; 560991</t>
+          <t>461960; 501963</t>
         </is>
       </c>
     </row>
